--- a/tasks/finalpool/yf-earnings-calendar-report/groundtruth_workspace/Stock_Financial_Summary.xlsx
+++ b/tasks/finalpool/yf-earnings-calendar-report/groundtruth_workspace/Stock_Financial_Summary.xlsx
@@ -514,7 +514,7 @@
         <v>22.431484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.28</v>
+        <v>0.0028</v>
       </c>
       <c r="H3" t="n">
         <v>10.82</v>
@@ -546,7 +546,7 @@
         <v>19.082195</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>0.0212</v>
       </c>
       <c r="H4" t="n">
         <v>11.04</v>
@@ -578,7 +578,7 @@
         <v>12.495573</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="H5" t="n">
         <v>20.03</v>
@@ -610,7 +610,7 @@
         <v>17.980968</v>
       </c>
       <c r="G6" t="n">
-        <v>2.75</v>
+        <v>0.0275</v>
       </c>
       <c r="H6" t="n">
         <v>6.7</v>
